--- a/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
+++ b/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
@@ -353,6 +353,9 @@
     <t xml:space="preserve">enable_serial_port_settings_via_escape_sequence</t>
   </si>
   <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">router1</t>
   </si>
   <si>
@@ -372,9 +375,6 @@
   </si>
   <si>
     <t xml:space="preserve">enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
   </si>
   <si>
     <t xml:space="preserve">router2</t>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>25</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>25</v>
@@ -2728,7 +2728,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>25</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>25</v>
@@ -2995,19 +2995,19 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
@@ -3017,10 +3017,10 @@
         <v>9600</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>7</v>
@@ -3029,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P2" s="15" t="s">
         <v>55</v>
@@ -3046,15 +3046,15 @@
         <v>55</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>25</v>
@@ -3066,7 +3066,7 @@
         <v>117</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -3076,10 +3076,10 @@
         <v>9600</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>7</v>
@@ -3088,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P3" s="15" t="s">
         <v>55</v>
@@ -3108,12 +3108,12 @@
         <v>118</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
@@ -3125,7 +3125,7 @@
         <v>120</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -3135,10 +3135,10 @@
         <v>9600</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>7</v>
@@ -3147,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P4" s="15" t="s">
         <v>55</v>
@@ -3164,15 +3164,15 @@
         <v>55</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>25</v>
@@ -3184,7 +3184,7 @@
         <v>122</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
@@ -3194,10 +3194,10 @@
         <v>9600</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>7</v>
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P5" s="15" t="s">
         <v>55</v>
@@ -3226,12 +3226,12 @@
         <v>118</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>25</v>
@@ -3240,10 +3240,10 @@
         <v>123</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -3253,10 +3253,10 @@
         <v>9600</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>7</v>
@@ -3265,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P6" s="15" t="s">
         <v>55</v>
@@ -3285,7 +3285,7 @@
         <v>118</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>25</v>
@@ -3483,10 +3483,10 @@
         <v>9600</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>7</v>
@@ -3495,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P2" s="15" t="s">
         <v>55</v>
@@ -3512,16 +3512,16 @@
         <v>55</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>25</v>
@@ -3547,10 +3547,10 @@
         <v>9600</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>7</v>
@@ -3559,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P3" s="15" t="s">
         <v>55</v>
@@ -3579,13 +3579,13 @@
         <v>118</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
@@ -3611,10 +3611,10 @@
         <v>9600</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>7</v>
@@ -3623,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P4" s="15" t="s">
         <v>55</v>
@@ -3640,16 +3640,16 @@
         <v>55</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>25</v>
@@ -3675,10 +3675,10 @@
         <v>9600</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>7</v>
@@ -3687,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P5" s="15" t="s">
         <v>55</v>
@@ -3707,7 +3707,7 @@
         <v>118</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X5" s="15"/>
     </row>
@@ -3823,7 +3823,7 @@
         <v>142</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E2" s="15" t="s">
         <v>143</v>
@@ -3852,7 +3852,7 @@
         <v>145</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>143</v>
@@ -3881,7 +3881,7 @@
         <v>146</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>143</v>
@@ -3918,7 +3918,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultColWidth="10.55078125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.36"/>
@@ -4001,7 +4001,7 @@
       <c r="T1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4013,54 +4013,54 @@
       <c r="D2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>115</v>
+      <c r="H2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="15" t="s">
@@ -4072,19 +4072,31 @@
       <c r="D3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="15" t="s">
         <v>168</v>
       </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
+      <c r="A4" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
@@ -4095,18 +4107,30 @@
       <c r="D4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="15" t="s">
         <v>168</v>
       </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -4118,19 +4142,31 @@
       <c r="D5" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="15" t="s">
         <v>166</v>
       </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
+      <c r="A6" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>25</v>
@@ -4141,19 +4177,31 @@
       <c r="D6" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="15" t="s">
         <v>168</v>
       </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
+      <c r="A7" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>25</v>
@@ -4164,18 +4212,30 @@
       <c r="D7" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="15" t="s">
         <v>168</v>
       </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -4187,18 +4247,30 @@
       <c r="D8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="15" t="s">
         <v>166</v>
       </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -4210,18 +4282,30 @@
       <c r="D9" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="15" t="s">
         <v>168</v>
       </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -4233,19 +4317,31 @@
       <c r="D10" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="15" t="s">
         <v>168</v>
       </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
+      <c r="A11" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>25</v>
@@ -4256,15 +4352,39 @@
       <c r="D11" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="15" t="s">
         <v>168</v>
       </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D18" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4357,7 +4477,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>55</v>
@@ -4375,16 +4495,16 @@
         <v>58</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N2" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="P2" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="P2" s="15" t="s">
-        <v>111</v>
-      </c>
       <c r="R2" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T2" s="15" t="n">
         <v>5</v>
@@ -4393,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>165</v>
@@ -4410,7 +4530,7 @@
         <v>128</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>182</v>
@@ -4419,7 +4539,7 @@
         <v>75</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>183</v>
@@ -4513,7 +4633,7 @@
         <v>8</v>
       </c>
       <c r="X5" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4832,7 +4952,7 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L43" s="15" t="s">
         <v>267</v>

--- a/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
+++ b/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="425">
   <si>
     <t xml:space="preserve">📘 Nodegrid Template – Overview &amp; Usage Guide</t>
   </si>
@@ -71,10 +71,16 @@
     <t xml:space="preserve">Contains USB serial configurations for virtual or physical devices.</t>
   </si>
   <si>
+    <t xml:space="preserve">Device_Permissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the Groups and their respective Device Access permissions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Discovery_Rules</t>
   </si>
   <si>
-    <t xml:space="preserve">Contains Port Discovery Rules, which are required to auto detect Serial and KVM ports on appliance, for example from Vertiv, Opengear, Raritan</t>
+    <t xml:space="preserve">Contains Port Discovery Rules, which are required to auto detect Serial and KVM ports on appliance, for example from Vertiv, Opengear, Raritan.</t>
   </si>
   <si>
     <t xml:space="preserve">Update Configuration Sheets</t>
@@ -107,7 +113,7 @@
     <t xml:space="preserve">NGM-Coordinator</t>
   </si>
   <si>
-    <t xml:space="preserve">127.0.0.10</t>
+    <t xml:space="preserve">127.0.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">22</t>
@@ -2080,7 +2086,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="11" t="s">
@@ -2098,8 +2104,15 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -2120,15 +2133,8 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
-      <c r="B14" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="12"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -2138,10 +2144,15 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="B15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="12"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -2151,11 +2162,18 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
+    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13"/>
@@ -2175,7 +2193,12 @@
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
     </row>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+    </row>
     <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2191,7 +2214,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2220,75 +2243,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>30</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>28</v>
       </c>
       <c r="F3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>27</v>
-      </c>
       <c r="E4" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="15"/>
     </row>
@@ -2336,496 +2359,496 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J2" s="15"/>
       <c r="K2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J3" s="15"/>
       <c r="K3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q6" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F9" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="16" t="s">
-        <v>87</v>
-      </c>
       <c r="I9" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2924,90 +2947,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
@@ -3017,10 +3040,10 @@
         <v>9600</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>7</v>
@@ -3029,44 +3052,44 @@
         <v>1</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q2" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R2" s="15"/>
       <c r="S2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T2" s="15"/>
       <c r="U2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -3076,10 +3099,10 @@
         <v>9600</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>7</v>
@@ -3088,44 +3111,44 @@
         <v>1</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R3" s="15"/>
       <c r="S3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T3" s="15"/>
       <c r="U3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -3135,10 +3158,10 @@
         <v>9600</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>7</v>
@@ -3147,44 +3170,44 @@
         <v>1</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R4" s="15"/>
       <c r="S4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T4" s="15"/>
       <c r="U4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
@@ -3194,10 +3217,10 @@
         <v>9600</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>7</v>
@@ -3206,44 +3229,44 @@
         <v>1</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R5" s="15"/>
       <c r="S5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T5" s="15"/>
       <c r="U5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -3253,10 +3276,10 @@
         <v>9600</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>7</v>
@@ -3265,27 +3288,27 @@
         <v>1</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P6" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q6" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R6" s="15"/>
       <c r="S6" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T6" s="15"/>
       <c r="U6" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V6" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3380,102 +3403,102 @@
   <sheetData>
     <row r="1" s="15" customFormat="true" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T1" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="U1" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="V1" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W1" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="X1" s="19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Y1" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
@@ -3483,10 +3506,10 @@
         <v>9600</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>7</v>
@@ -3495,51 +3518,51 @@
         <v>1</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R2" s="15"/>
       <c r="S2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T2" s="15"/>
       <c r="U2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>132</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>130</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
@@ -3547,10 +3570,10 @@
         <v>9600</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>7</v>
@@ -3559,51 +3582,51 @@
         <v>1</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R3" s="15"/>
       <c r="S3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T3" s="15"/>
       <c r="U3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -3611,10 +3634,10 @@
         <v>9600</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>7</v>
@@ -3623,51 +3646,51 @@
         <v>1</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R4" s="15"/>
       <c r="S4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T4" s="15"/>
       <c r="U4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -3675,10 +3698,10 @@
         <v>9600</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>7</v>
@@ -3687,27 +3710,27 @@
         <v>1</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R5" s="15"/>
       <c r="S5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T5" s="15"/>
       <c r="U5" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X5" s="15"/>
     </row>
@@ -3785,118 +3808,118 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>143</v>
-      </c>
       <c r="F3" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>144</v>
-      </c>
       <c r="G4" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3942,141 +3965,141 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="T1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>168</v>
@@ -4096,25 +4119,25 @@
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -4131,25 +4154,25 @@
     </row>
     <row r="5" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -4166,25 +4189,25 @@
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D6" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>167</v>
-      </c>
       <c r="G6" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -4201,25 +4224,25 @@
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D7" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>170</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>168</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -4236,25 +4259,25 @@
     </row>
     <row r="8" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -4271,22 +4294,22 @@
     </row>
     <row r="9" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>168</v>
@@ -4306,22 +4329,22 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>168</v>
@@ -4341,22 +4364,22 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="E11" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>169</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>167</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>168</v>
@@ -4427,84 +4450,84 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N1" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="R1" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="X1" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="T2" s="15" t="n">
         <v>5</v>
@@ -4513,48 +4536,48 @@
         <v>1</v>
       </c>
       <c r="X2" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N3" s="15" t="n">
         <v>9600</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="T3" s="15" t="n">
         <v>6</v>
@@ -4563,68 +4586,68 @@
         <v>2</v>
       </c>
       <c r="X3" s="15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N4" s="15" t="n">
         <v>19200</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="T4" s="15" t="n">
         <v>7</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N5" s="15" t="n">
         <v>57600</v>
@@ -4633,21 +4656,21 @@
         <v>8</v>
       </c>
       <c r="X5" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N6" s="15" t="n">
         <v>38400</v>
@@ -4655,13 +4678,13 @@
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>115200</v>
@@ -4669,10 +4692,10 @@
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E8" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>230400</v>
@@ -4680,1021 +4703,1021 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E9" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E10" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E13" s="15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E14" s="15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E15" s="15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E16" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E18" s="15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E19" s="15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="15" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E22" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="15" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E28" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E29" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E30" s="15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="15" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E33" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E36" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="15" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E41" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E44" s="15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E45" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E46" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E47" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E48" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E49" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E50" s="15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E51" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E52" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L52" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E53" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E54" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E55" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L56" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E58" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L58" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E59" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E60" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L60" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E61" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E62" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L62" s="15" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E63" s="15" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E64" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L64" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E65" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E66" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L66" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L67" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L68" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L69" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L70" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L71" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L72" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L73" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L74" s="15" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L75" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L76" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L77" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L78" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L79" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L80" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L81" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L82" s="15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L83" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L84" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L85" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L86" s="15" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L87" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L88" s="15" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L89" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L90" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L91" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L92" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L93" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L94" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L95" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L96" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L97" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L98" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L99" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L100" s="15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L101" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L102" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L103" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L104" s="15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L105" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L106" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L107" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L108" s="15" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L109" s="15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L110" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L111" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L112" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L113" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L114" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L115" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L116" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L117" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L118" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L119" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L120" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L121" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L122" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L123" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L124" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L125" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L126" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L127" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L128" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L129" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L130" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L131" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L132" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L133" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L134" s="15" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L135" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L136" s="15" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L137" s="15" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L138" s="15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L139" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L140" s="15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L141" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L142" s="15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L143" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L144" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L145" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L146" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L147" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L148" s="15" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L149" s="15" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L150" s="15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L151" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L152" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L153" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L154" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L155" s="15" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L156" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L157" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L158" s="15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L159" s="15" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L160" s="15" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L161" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L162" s="15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L163" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L164" s="15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L165" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L166" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L167" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L168" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L169" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L170" s="15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L171" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L172" s="15" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L173" s="15" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L174" s="15" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L175" s="15" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L176" s="15" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L177" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>

--- a/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
+++ b/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="443">
   <si>
     <t xml:space="preserve">📘 Nodegrid Template – Overview &amp; Usage Guide</t>
   </si>
@@ -158,6 +158,9 @@
     <t xml:space="preserve">username</t>
   </si>
   <si>
+    <t xml:space="preserve">credential</t>
+  </si>
+  <si>
     <t xml:space="preserve">password</t>
   </si>
   <si>
@@ -179,6 +182,30 @@
     <t xml:space="preserve">port_number</t>
   </si>
   <si>
+    <t xml:space="preserve">allow_ssh_protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh_port</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allow_pre-shared_ssh_key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh_key_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh_private_key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh_public_key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_discover_ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rebounce</t>
+  </si>
+  <si>
     <t xml:space="preserve">cf_Rack_Location</t>
   </si>
   <si>
@@ -581,6 +608,12 @@
     <t xml:space="preserve">128technology.png</t>
   </si>
   <si>
+    <t xml:space="preserve">ask_during_login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecdsa_256</t>
+  </si>
+  <si>
     <t xml:space="preserve">air_flow-temperature.png</t>
   </si>
   <si>
@@ -605,6 +638,12 @@
     <t xml:space="preserve">door_status</t>
   </si>
   <si>
+    <t xml:space="preserve">set_now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecdsa_384</t>
+  </si>
+  <si>
     <t xml:space="preserve">apc.png</t>
   </si>
   <si>
@@ -620,25 +659,40 @@
     <t xml:space="preserve">DCD</t>
   </si>
   <si>
+    <t xml:space="preserve">ecdsa_521</t>
+  </si>
+  <si>
     <t xml:space="preserve">device_console</t>
   </si>
   <si>
     <t xml:space="preserve">apple_black.png</t>
   </si>
   <si>
+    <t xml:space="preserve">ed25519</t>
+  </si>
+  <si>
     <t xml:space="preserve">arista.png</t>
   </si>
   <si>
     <t xml:space="preserve">ttyS5</t>
   </si>
   <si>
+    <t xml:space="preserve">rsa_1024</t>
+  </si>
+  <si>
     <t xml:space="preserve">aruba.png</t>
   </si>
   <si>
     <t xml:space="preserve">ttyS6</t>
   </si>
   <si>
+    <t xml:space="preserve">rsa_2048</t>
+  </si>
+  <si>
     <t xml:space="preserve">ttyS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rsa_4096</t>
   </si>
   <si>
     <t xml:space="preserve">ttyS8</t>
@@ -1640,9 +1694,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="local_ip" displayName="local_ip" ref="A1:R12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:R12"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="local_ip" displayName="local_ip" ref="A1:AA12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:AA12"/>
+  <tableColumns count="27">
     <tableColumn id="1" name="Export"/>
     <tableColumn id="2" name="ansible_inventory_name"/>
     <tableColumn id="3" name="name"/>
@@ -1652,15 +1706,24 @@
     <tableColumn id="7" name="ip_address"/>
     <tableColumn id="8" name="port"/>
     <tableColumn id="9" name="username"/>
-    <tableColumn id="10" name="password"/>
-    <tableColumn id="11" name="enable_device_state_detection_based_on_network_traffic"/>
-    <tableColumn id="12" name="multisession"/>
-    <tableColumn id="13" name="icon"/>
-    <tableColumn id="14" name="mode"/>
-    <tableColumn id="15" name="end_point"/>
-    <tableColumn id="16" name="port_number"/>
-    <tableColumn id="17" name="cf_Rack_Location"/>
-    <tableColumn id="18" name="cf_custom_field2"/>
+    <tableColumn id="10" name="credential"/>
+    <tableColumn id="11" name="password"/>
+    <tableColumn id="12" name="enable_device_state_detection_based_on_network_traffic"/>
+    <tableColumn id="13" name="multisession"/>
+    <tableColumn id="14" name="icon"/>
+    <tableColumn id="15" name="mode"/>
+    <tableColumn id="16" name="end_point"/>
+    <tableColumn id="17" name="port_number"/>
+    <tableColumn id="18" name="allow_ssh_protocol"/>
+    <tableColumn id="19" name="ssh_port"/>
+    <tableColumn id="20" name="allow_pre-shared_ssh_key"/>
+    <tableColumn id="21" name="ssh_key_type"/>
+    <tableColumn id="22" name="ssh_private_key"/>
+    <tableColumn id="23" name="ssh_public_key"/>
+    <tableColumn id="24" name="mgmt_discover_ports"/>
+    <tableColumn id="25" name="rebounce"/>
+    <tableColumn id="26" name="cf_Rack_Location"/>
+    <tableColumn id="27" name="cf_custom_field2"/>
   </tableColumns>
 </table>
 </file>
@@ -2335,7 +2398,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.33"/>
@@ -2347,14 +2410,23 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="33.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="15" width="22.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="15" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="17.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2412,6 +2484,33 @@
       <c r="R1" s="14" t="s">
         <v>51</v>
       </c>
+      <c r="S1" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="V1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="W1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="X1" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y1" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA1" s="14" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
@@ -2421,42 +2520,42 @@
         <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K2" s="15"/>
       <c r="L2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" s="15" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2467,42 +2566,42 @@
         <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K3" s="15"/>
       <c r="L3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>66</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA3" s="15" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2513,45 +2612,45 @@
         <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K4" s="15"/>
       <c r="L4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q4" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R4" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>68</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z4" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA4" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
         <v>26</v>
       </c>
@@ -2559,47 +2658,47 @@
         <v>27</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K5" s="15"/>
       <c r="L5" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z5" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA5" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
         <v>26</v>
       </c>
@@ -2607,50 +2706,50 @@
         <v>27</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K6" s="15"/>
       <c r="L6" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="P6" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R6" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z6" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA6" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
         <v>31</v>
       </c>
@@ -2658,50 +2757,50 @@
         <v>27</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E7" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>75</v>
-      </c>
       <c r="I7" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K7" s="15"/>
       <c r="L7" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="P7" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R7" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z7" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA7" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
         <v>31</v>
       </c>
@@ -2709,47 +2808,47 @@
         <v>27</v>
       </c>
       <c r="C8" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q8" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R8" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z8" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA8" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
         <v>31</v>
       </c>
@@ -2757,50 +2856,50 @@
         <v>27</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F9" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="O9" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="P9" s="1" t="n">
+      <c r="Q9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z9" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA9" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
         <v>31</v>
       </c>
@@ -2808,74 +2907,81 @@
         <v>27</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K10" s="15"/>
       <c r="L10" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="P10" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>67</v>
+        <v>86</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="S10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="Z10" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA10" s="15" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15"/>
       <c r="D11" s="15"/>
-      <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15"/>
       <c r="D12" s="15"/>
-      <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="11">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="R2:R1010 T2:T1010 X2:Y1010" type="list">
+      <formula1>Lookup_Table!$C$2:$C$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H2:H12" type="whole">
       <formula1>1</formula1>
       <formula2>65500</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="P2:P9 P11:P12" type="whole">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="Q2:Q9 S2:S9 V2:W9 Q11:Q12 S11:S12 V11:W12" type="whole">
       <formula1>1</formula1>
       <formula2>96</formula2>
     </dataValidation>
@@ -2887,20 +2993,28 @@
       <formula1>Lookup_Table!$A$2:$A$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A12 K2:L12" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A12 L2:M12" type="list">
       <formula1>Lookup_Table!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M2:M12" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N12" type="list">
       <formula1>Lookup_Table!$E$2:$E$202</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N12" type="list">
-      <formula1>Lookup_Table!$G$2:$G$3</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="P2:P12" type="list">
+      <formula1>Lookup_Table!$J$2:$J$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O12" type="list">
-      <formula1>Lookup_Table!$J$2:$J$6</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J2:J1010" type="list">
+      <formula1>Lookup_Table!$AD$2:$AD$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O1010" type="list">
+      <formula1>Lookup_Table!$G$2:$G$4</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="U2:U1010" type="list">
+      <formula1>Lookup_Table!$AF$2:$AF$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -2956,7 +3070,7 @@
         <v>36</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>37</v>
@@ -2971,66 +3085,66 @@
         <v>42</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
@@ -3040,10 +3154,10 @@
         <v>9600</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>7</v>
@@ -3052,44 +3166,44 @@
         <v>1</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q2" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R2" s="15"/>
       <c r="S2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T2" s="15"/>
       <c r="U2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
@@ -3099,10 +3213,10 @@
         <v>9600</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>7</v>
@@ -3111,44 +3225,44 @@
         <v>1</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q3" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R3" s="15"/>
       <c r="S3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T3" s="15"/>
       <c r="U3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D4" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>122</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>113</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -3158,10 +3272,10 @@
         <v>9600</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>7</v>
@@ -3170,44 +3284,44 @@
         <v>1</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q4" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R4" s="15"/>
       <c r="S4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T4" s="15"/>
       <c r="U4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
@@ -3217,10 +3331,10 @@
         <v>9600</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>7</v>
@@ -3229,44 +3343,44 @@
         <v>1</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R5" s="15"/>
       <c r="S5" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T5" s="15"/>
       <c r="U5" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -3276,10 +3390,10 @@
         <v>9600</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>7</v>
@@ -3288,27 +3402,27 @@
         <v>1</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P6" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q6" s="15" t="n">
         <v>3</v>
       </c>
       <c r="R6" s="15"/>
       <c r="S6" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T6" s="15"/>
       <c r="U6" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V6" s="15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3412,7 +3526,7 @@
         <v>36</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>37</v>
@@ -3427,78 +3541,78 @@
         <v>42</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T1" s="19" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="U1" s="19" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="V1" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W1" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X1" s="19" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="Y1" s="19" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
@@ -3506,10 +3620,10 @@
         <v>9600</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>7</v>
@@ -3518,51 +3632,51 @@
         <v>1</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R2" s="15"/>
       <c r="S2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T2" s="15"/>
       <c r="U2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V2" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="X2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
@@ -3570,10 +3684,10 @@
         <v>9600</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>7</v>
@@ -3582,51 +3696,51 @@
         <v>1</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R3" s="15"/>
       <c r="S3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T3" s="15"/>
       <c r="U3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="X3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -3634,10 +3748,10 @@
         <v>9600</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>7</v>
@@ -3646,51 +3760,51 @@
         <v>1</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R4" s="15"/>
       <c r="S4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T4" s="15"/>
       <c r="U4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="X4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -3698,10 +3812,10 @@
         <v>9600</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>7</v>
@@ -3710,27 +3824,27 @@
         <v>1</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="R5" s="15"/>
       <c r="S5" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="T5" s="15"/>
       <c r="U5" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="X5" s="15"/>
     </row>
@@ -3814,25 +3928,25 @@
         <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3843,25 +3957,25 @@
         <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3872,25 +3986,25 @@
         <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3901,25 +4015,25 @@
         <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3971,55 +4085,55 @@
         <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="T1" s="14"/>
     </row>
@@ -4031,55 +4145,55 @@
         <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4090,19 +4204,19 @@
         <v>27</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
@@ -4125,19 +4239,19 @@
         <v>27</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -4160,19 +4274,19 @@
         <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -4195,19 +4309,19 @@
         <v>27</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -4230,19 +4344,19 @@
         <v>27</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -4265,19 +4379,19 @@
         <v>27</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -4300,19 +4414,19 @@
         <v>27</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -4335,19 +4449,19 @@
         <v>27</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
@@ -4370,19 +4484,19 @@
         <v>27</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
@@ -4426,7 +4540,7 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB177"/>
+  <dimension ref="A1:AF177"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="21.5"/>
@@ -4446,6 +4560,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="2.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="13.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="12.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="2.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4453,81 +4569,87 @@
         <v>37</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N1" s="15" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="R1" s="15" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="X1" s="15" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF1" s="0" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="R2" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="T2" s="15" t="n">
         <v>5</v>
@@ -4536,48 +4658,54 @@
         <v>1</v>
       </c>
       <c r="X2" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF2" s="0" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="N3" s="15" t="n">
         <v>9600</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="T3" s="15" t="n">
         <v>6</v>
@@ -4586,68 +4714,83 @@
         <v>2</v>
       </c>
       <c r="X3" s="15" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="AF3" s="0" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>192</v>
+        <v>205</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>86</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="N4" s="15" t="n">
         <v>19200</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="T4" s="15" t="n">
         <v>7</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
+      </c>
+      <c r="AF4" s="0" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="N5" s="15" t="n">
         <v>57600</v>
@@ -4656,1068 +4799,1080 @@
         <v>8</v>
       </c>
       <c r="X5" s="15" t="s">
-        <v>114</v>
+        <v>123</v>
+      </c>
+      <c r="AF5" s="0" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="N6" s="15" t="n">
         <v>38400</v>
       </c>
+      <c r="AF6" s="0" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>115200</v>
       </c>
+      <c r="AF7" s="0" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E8" s="15" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>230400</v>
       </c>
+      <c r="AF8" s="0" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E9" s="15" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E10" s="15" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="15" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="15" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E13" s="15" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E14" s="15" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E15" s="15" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E16" s="15" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="15" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E18" s="15" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E19" s="15" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="15" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="15" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E22" s="15" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="15" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="15" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="15" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="15" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="15" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E28" s="15" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E29" s="15" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E30" s="15" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="15" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="15" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E33" s="15" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="15" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="15" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E36" s="15" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="15" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="15" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="15" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="15" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E41" s="15" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="15" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E44" s="15" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E45" s="15" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E46" s="15" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E47" s="15" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E48" s="15" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E49" s="15" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E50" s="15" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E51" s="15" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E52" s="15" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="L52" s="15" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E53" s="15" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E54" s="15" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E55" s="15" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L56" s="15" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="15" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E58" s="15" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="L58" s="15" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E59" s="15" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E60" s="15" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="L60" s="15" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E61" s="15" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E62" s="15" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="L62" s="15" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E63" s="15" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E64" s="15" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="L64" s="15" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E65" s="15" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E66" s="15" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="L66" s="15" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L67" s="15" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L68" s="15" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L69" s="15" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L70" s="15" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L71" s="15" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L72" s="15" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L73" s="15" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L74" s="15" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L75" s="15" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L76" s="15" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L77" s="15" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L78" s="15" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L79" s="15" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L80" s="15" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L81" s="15" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L82" s="15" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L83" s="15" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L84" s="15" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L85" s="15" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L86" s="15" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L87" s="15" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L88" s="15" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L89" s="15" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L90" s="15" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L91" s="15" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L92" s="15" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L93" s="15" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L94" s="15" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L95" s="15" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L96" s="15" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L97" s="15" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L98" s="15" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L99" s="15" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L100" s="15" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L101" s="15" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L102" s="15" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L103" s="15" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L104" s="15" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L105" s="15" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L106" s="15" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L107" s="15" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L108" s="15" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L109" s="15" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L110" s="15" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L111" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L112" s="15" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L113" s="15" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L114" s="15" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L115" s="15" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L116" s="15" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L117" s="15" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L118" s="15" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L119" s="15" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L120" s="15" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L121" s="15" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L122" s="15" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L123" s="15" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L124" s="15" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L125" s="15" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L126" s="15" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L127" s="15" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L128" s="15" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L129" s="15" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L130" s="15" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L131" s="15" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L132" s="15" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L133" s="15" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L134" s="15" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L135" s="15" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L136" s="15" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L137" s="15" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L138" s="15" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L139" s="15" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L140" s="15" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L141" s="15" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L142" s="15" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L143" s="15" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L144" s="15" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L145" s="15" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L146" s="15" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L147" s="15" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L148" s="15" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L149" s="15" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L150" s="15" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L151" s="15" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L152" s="15" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L153" s="15" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L154" s="15" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L155" s="15" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L156" s="15" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L157" s="15" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L158" s="15" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L159" s="15" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L160" s="15" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L161" s="15" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L162" s="15" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L163" s="15" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L164" s="15" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L165" s="15" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L166" s="15" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L167" s="15" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L168" s="15" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L169" s="15" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L170" s="15" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L171" s="15" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L172" s="15" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L173" s="15" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L174" s="15" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L175" s="15" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L176" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L177" s="15" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>

--- a/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
+++ b/examples/playbooks/system-roles/Migration_Automation_Managed_Devices/Nodegrid_Importer_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
@@ -17,7 +17,7 @@
     <sheet name="Lookup_Table" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">IP_Devices!$A$1:$AN$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">IP_Devices!$A$1:$AQ$3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +34,7 @@
     <author>Rene Neumann</author>
   </authors>
   <commentList>
-    <comment ref="C77" authorId="0">
+    <comment ref="C93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -65,14 +65,14 @@
               <xdr:from>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
-                <xdr:row>74</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:row>91</xdr:row>
+                <xdr:rowOff>38</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>-648</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>9</xdr:rowOff>
+                <xdr:colOff>-1026</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -80,7 +80,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="C78" authorId="0">
+    <comment ref="C94" authorId="0">
       <text>
         <r>
           <rPr>
@@ -109,14 +109,14 @@
               <xdr:from>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
-                <xdr:row>75</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:row>91</xdr:row>
+                <xdr:rowOff>61</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>-589</xdr:colOff>
-                <xdr:row>83</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
+                <xdr:colOff>-967</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -124,7 +124,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="C86" authorId="0">
+    <comment ref="C102" authorId="0">
       <text>
         <r>
           <rPr>
@@ -155,14 +155,14 @@
               <xdr:from>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>58</xdr:colOff>
-                <xdr:row>83</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
+                <xdr:row>99</xdr:row>
+                <xdr:rowOff>15</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>-649</xdr:colOff>
-                <xdr:row>88</xdr:row>
-                <xdr:rowOff>7</xdr:rowOff>
+                <xdr:colOff>-1027</xdr:colOff>
+                <xdr:row>107</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -460,6 +460,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Rene Neumann</author>
+    <author>Unknown Author</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -1239,7 +1240,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>21</xdr:col>
-                <xdr:colOff>11</xdr:colOff>
+                <xdr:colOff>75</xdr:colOff>
                 <xdr:row>6</xdr:row>
                 <xdr:rowOff>6</xdr:rowOff>
               </xdr:to>
@@ -1284,9 +1285,42 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>21</xdr:col>
-                <xdr:colOff>29</xdr:colOff>
+                <xdr:colOff>95</xdr:colOff>
                 <xdr:row>8</xdr:row>
                 <xdr:rowOff>6</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="AC1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Default: %APPLIANCE_%IP_%PORT</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>29</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>30</xdr:col>
+                <xdr:colOff>-10</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>-15</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1555,7 +1589,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="528">
   <si>
     <t xml:space="preserve">📘 Nodegrid Template – Overview &amp; Usage Guide</t>
   </si>
@@ -1563,7 +1597,7 @@
     <t xml:space="preserve">Template Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Last Updated: 17/12/2025</t>
+    <t xml:space="preserve">Last Updated: 22/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">🔍 Purpose</t>
@@ -1698,7 +1732,7 @@
     <t xml:space="preserve">type</t>
   </si>
   <si>
-    <t xml:space="preserve">Device type to be used for the managed device. This defines the connection capabilties.</t>
+    <t xml:space="preserve">Device type to be used for the managed device. This defines the connection capabilities</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
@@ -1746,7 +1780,7 @@
     <t xml:space="preserve">mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Defines the state (mode) of the device after it was imported.  Disabled means device is not active and no connections can be made. Enabled: connections are possiable, a permanent connection is kept open. on-demand: connections are possiable, connections are created when needed Default: disabled, Recommended: on-demand</t>
+    <t xml:space="preserve">Defines the state (mode) of the device after it was imported.  Disabled means device is not active and no connections can be made. Enabled: connections are possible, a permanent connection is kept open. on-demand: connections are possible, connections are created when needed Default: disabled, Recommended: on-demand</t>
   </si>
   <si>
     <t xml:space="preserve">on-demand</t>
@@ -1770,7 +1804,7 @@
     <t xml:space="preserve">multisession</t>
   </si>
   <si>
-    <t xml:space="preserve">controlls the if multiple users can connect at the same time to the device or not. Dafault: yes</t>
+    <t xml:space="preserve">controls the if multiple users can connect at the same time to the device or not. Default: yes</t>
   </si>
   <si>
     <t xml:space="preserve">read-write_multisession</t>
@@ -1794,13 +1828,13 @@
     <t xml:space="preserve">port_number</t>
   </si>
   <si>
-    <t xml:space="preserve">When end_point indicates that the device represents a port on a appliance. Then this field indicates the port number on the appliance, which needs to be used to reach the device. This is Typically a numerical value, like 1,2,3 etc.</t>
+    <t xml:space="preserve">When end-point indicates that the device represents a port on a appliance. Then this field indicates the port number on the appliance, which needs to be used to reach the device. This is Typically a numerical value, like 1,2,3 etc.</t>
   </si>
   <si>
     <t xml:space="preserve">cf_Rack_Location</t>
   </si>
   <si>
-    <t xml:space="preserve">custom fields can be assosiated with the devices. To import custom data, change the column header to reflect teh filed name with a leading cf_ example: Field Name: Rack_Loaction, column header name: cf_Rack_Location IMPORTANT: for each device an appropiate cell was be provided, if the value should be blank, use blank or n/a. If no custom values need to be imported then this column can be deleted.</t>
+    <t xml:space="preserve">custom fields can be associated with the devices. To import custom data, change the column header to reflect teh filed name with a leading cf_ example: Field Name: Rack_Loaction, column header name: cf_Rack_Location IMPORTANT: for each device an appropriate cell was be provided, if the value should be blank, use blank or n/a. If no custom values need to be imported then this column can be deleted.</t>
   </si>
   <si>
     <t xml:space="preserve">allow_ssh_protocol</t>
@@ -1839,6 +1873,102 @@
     <t xml:space="preserve">ssh public key to be used for the authentication</t>
   </si>
   <si>
+    <t xml:space="preserve">mgmt_discover_ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls the discovery ports automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_discover_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the discovery ports interval in minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_discovered_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the discovered name behavior: Inherit from appliance or pattern name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_pattern_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the discovered pattern name. Default value: %APPLIANCE_%IP_%PORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_purge_disabled_end_point_ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enables the purging of disabled end points ports.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define the action for the purge disabled end point ports.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enables/Disables the SNMP option for the device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmp_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP version: v1, v2, v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmp_community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP community for versions v1 and v2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmpv3_username</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP username for version v3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmpv3_security_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP security level for version v3. Options are: authnopriv, authpriv, noauthnopriv.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmpv3_authentication_algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP authentication algorithm for version v3. Options are: md5, sha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmpv3_authentication_password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP authentication password for version v3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmpv3_privacy_algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP security level for version v3. Options are: aes, des.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mgmt_snmpv3_privacy_password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defines the SNMP privacy password for version v3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rebounce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enables/Disables the action of disabling and enabling of the device after it being created.</t>
+  </si>
+  <si>
     <t xml:space="preserve">port_name</t>
   </si>
   <si>
@@ -1896,10 +2026,10 @@
     <t xml:space="preserve">data_flow_scan_interval</t>
   </si>
   <si>
-    <t xml:space="preserve">the interval in secounds which will be used to probe the device state if it is based on the data_flow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controls  if multiple users can connect at the same time to the device or not. Dafault: yes</t>
+    <t xml:space="preserve">the interval in seconds which will be used to probe the device state if it is based on the data_flow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls  if multiple users can connect at the same time to the device or not. Default: yes</t>
   </si>
   <si>
     <t xml:space="preserve">enable_serial_port_settings_via_escape_sequence</t>
@@ -1908,7 +2038,7 @@
     <t xml:space="preserve">Controls if serial port settings can be overwritten on an adhoc bais through a open device session.</t>
   </si>
   <si>
-    <t xml:space="preserve">Defines the state (mode) of the device after it was imported.  Disabled means device is not active and no connections can be made. Enabled: connections are possiable, a permanent connection is kept open. on-demand: connections are possiable, connections are created when needed Default: disabled, Recommended: enabled</t>
+    <t xml:space="preserve">Defines the state (mode) of the device after it was imported.  Disabled means device is not active and no connections can be made. Enabled: connections are possible, a permanent connection is kept open. on-demand: connections are possible, connections are created when needed Default: disabled, Recommended: enabled</t>
   </si>
   <si>
     <t xml:space="preserve">enabled</t>
@@ -1956,7 +2086,7 @@
     <t xml:space="preserve">inherit_appliance_credentials</t>
   </si>
   <si>
-    <t xml:space="preserve">Controles if the device connection credentials should be used from the template or the appliance to which the port is connected to. Default: no</t>
+    <t xml:space="preserve">Controls if the device connection credentials should be used from the template or the appliance to which the port is connected to. Default: no</t>
   </si>
   <si>
     <t xml:space="preserve">Device_Permissions</t>
@@ -2070,45 +2200,6 @@
     <t xml:space="preserve">web_url</t>
   </si>
   <si>
-    <t xml:space="preserve">mgmt_discover_ports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmp_version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmp_community</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmpv3_username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmpv3_security_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmpv3_authentication_algorithm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmpv3_authentication_password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmpv3_privacy_algorithm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_snmpv3_privacy_password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_purge_disabled_end_point_ports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgmt_action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rebounce</t>
-  </si>
-  <si>
     <t xml:space="preserve">cf_custom_field2</t>
   </si>
   <si>
@@ -2133,9 +2224,6 @@
     <t xml:space="preserve">appliance</t>
   </si>
   <si>
-    <t xml:space="preserve">na</t>
-  </si>
-  <si>
     <t xml:space="preserve">EXAMPLE-DEVICE</t>
   </si>
   <si>
@@ -2271,6 +2359,24 @@
     <t xml:space="preserve">ecdsa_256</t>
   </si>
   <si>
+    <t xml:space="preserve">inherit_from_appliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disable_ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">authnopriv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">md5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aes</t>
+  </si>
+  <si>
     <t xml:space="preserve">usb_serialb</t>
   </si>
   <si>
@@ -2301,6 +2407,24 @@
     <t xml:space="preserve">ecdsa_384</t>
   </si>
   <si>
+    <t xml:space="preserve">use_pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remove_ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">authpriv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">des</t>
+  </si>
+  <si>
     <t xml:space="preserve">console_server_nodegrid</t>
   </si>
   <si>
@@ -2323,6 +2447,12 @@
   </si>
   <si>
     <t xml:space="preserve">ecdsa_521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noauthnopriv</t>
   </si>
   <si>
     <t xml:space="preserve">apple_black.png</t>
@@ -3238,152 +3368,148 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3750,1732 +3876,1985 @@
   <dimension ref="A2:M1048576"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="88.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="130.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.5"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="11" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="11" t="s">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="11" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="11" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="13" t="s">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="A13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="A14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="2"/>
+      <c r="B15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17" t="s">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+    </row>
+    <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G20" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="18" t="s">
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="18"/>
-      <c r="C22" s="19" t="s">
+    <row r="22" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="22" t="s">
+      <c r="F22" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="18"/>
-      <c r="C23" s="19" t="s">
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="20"/>
+      <c r="C23" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="22" t="s">
+      <c r="F23" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="18"/>
-      <c r="C24" s="19" t="s">
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="20"/>
+      <c r="C24" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="22" t="n">
+      <c r="E24" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="24" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="18"/>
-      <c r="C25" s="19" t="s">
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="20"/>
+      <c r="C25" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="22" t="s">
+      <c r="E25" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="18"/>
-      <c r="C26" s="19" t="s">
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="20"/>
+      <c r="C26" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="22"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="18" t="s">
+      <c r="E26" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="24"/>
+    </row>
+    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="22" t="s">
+      <c r="F27" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="18"/>
-      <c r="C28" s="19" t="s">
+    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="20"/>
+      <c r="C28" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G28" s="22"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="18"/>
-      <c r="C29" s="19" t="s">
+      <c r="F28" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="20"/>
+      <c r="C29" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="22"/>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="18"/>
-      <c r="C30" s="19" t="s">
+      <c r="F29" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="20"/>
+      <c r="C30" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" s="22"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="18"/>
-      <c r="C31" s="19" t="s">
+      <c r="F30" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="20"/>
+      <c r="C31" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G31" s="22"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="18"/>
-      <c r="C32" s="19" t="s">
+      <c r="E31" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="20"/>
+      <c r="C32" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F32" s="22" t="s">
+      <c r="E32" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="22"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="18"/>
-      <c r="C33" s="19" t="s">
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="20"/>
+      <c r="C33" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G33" s="22"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="18"/>
-      <c r="C34" s="19" t="s">
+      <c r="F33" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="20"/>
+      <c r="C34" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="26" t="s">
+      <c r="D34" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="22" t="s">
+      <c r="E34" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="22"/>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="18"/>
-      <c r="C35" s="19" t="s">
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="20"/>
+      <c r="C35" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="22" t="s">
+      <c r="E35" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="22"/>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="18"/>
-      <c r="C36" s="19" t="s">
+      <c r="G35" s="24"/>
+    </row>
+    <row r="36" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="20"/>
+      <c r="C36" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="22" t="s">
+      <c r="E36" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G36" s="22"/>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="18"/>
-      <c r="C37" s="19" t="s">
+      <c r="G36" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="20"/>
+      <c r="C37" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="E37" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F37" s="22" t="s">
+      <c r="E37" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="22"/>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="18"/>
-      <c r="C38" s="19" t="s">
+      <c r="G37" s="24"/>
+    </row>
+    <row r="38" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="20"/>
+      <c r="C38" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D38" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E38" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="22" t="s">
+      <c r="E38" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="18"/>
-      <c r="C39" s="19" t="s">
+    <row r="39" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="20"/>
+      <c r="C39" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E39" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="22" t="s">
+      <c r="E39" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="18"/>
-      <c r="C40" s="19" t="s">
+    <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="20"/>
+      <c r="C40" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22" t="s">
+      <c r="E40" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G40" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="18"/>
-      <c r="C41" s="19" t="s">
+    <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="20"/>
+      <c r="C41" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F41" s="22" t="s">
+      <c r="E41" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="18"/>
-      <c r="C42" s="19" t="s">
+    <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="20"/>
+      <c r="C42" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D42" s="26" t="s">
+      <c r="D42" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E42" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="22" t="s">
+      <c r="E42" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G42" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="18"/>
-      <c r="C43" s="19" t="s">
+    <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="20"/>
+      <c r="C43" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E43" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F43" s="22" t="s">
+      <c r="E43" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G43" s="22"/>
-    </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="18"/>
-      <c r="C44" s="19" t="s">
+      <c r="G43" s="24"/>
+    </row>
+    <row r="44" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="20"/>
+      <c r="C44" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D44" s="26" t="s">
+      <c r="D44" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F44" s="22" t="s">
+      <c r="E44" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G44" s="22"/>
-    </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="18"/>
-      <c r="C45" s="19" t="s">
+      <c r="G44" s="24"/>
+    </row>
+    <row r="45" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="20"/>
+      <c r="C45" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="26" t="s">
+      <c r="D45" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F45" s="22" t="s">
+      <c r="E45" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G45" s="22"/>
-    </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="18"/>
-      <c r="C46" s="19" t="s">
+      <c r="G45" s="24"/>
+    </row>
+    <row r="46" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="20"/>
+      <c r="C46" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="26" t="s">
+      <c r="D46" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="E46" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="22" t="s">
+      <c r="E46" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G46" s="22"/>
-    </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="18"/>
-      <c r="C47" s="27" t="s">
+      <c r="G46" s="24"/>
+    </row>
+    <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="20"/>
+      <c r="C47" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="26" t="s">
+      <c r="D47" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E47" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F47" s="22" t="s">
+      <c r="E47" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G47" s="22"/>
-    </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="18"/>
-      <c r="C48" s="27" t="s">
+      <c r="G47" s="24"/>
+    </row>
+    <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="20"/>
+      <c r="C48" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="26" t="s">
+      <c r="D48" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E48" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" s="22" t="s">
+      <c r="E48" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G48" s="22"/>
-    </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="18"/>
-      <c r="C49" s="27" t="s">
+      <c r="G48" s="24"/>
+    </row>
+    <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="20"/>
+      <c r="C49" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="26" t="s">
+      <c r="D49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E49" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F49" s="22" t="s">
+      <c r="E49" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G49" s="22"/>
-    </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="18"/>
-      <c r="C50" s="27" t="s">
+      <c r="G49" s="24"/>
+    </row>
+    <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="20"/>
+      <c r="C50" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="26" t="s">
+      <c r="D50" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E50" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="22" t="s">
+      <c r="E50" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G50" s="22"/>
-    </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="18"/>
-      <c r="C51" s="27" t="s">
+      <c r="G50" s="24"/>
+    </row>
+    <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="20"/>
+      <c r="C51" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="26" t="s">
+      <c r="D51" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E51" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" s="22" t="s">
+      <c r="E51" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G51" s="22"/>
-    </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="18"/>
-      <c r="C52" s="27" t="s">
+      <c r="G51" s="24"/>
+    </row>
+    <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="20"/>
+      <c r="C52" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="26" t="s">
+      <c r="D52" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="E52" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F52" s="22" t="s">
+      <c r="E52" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G52" s="22"/>
-    </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="18" t="s">
+      <c r="G52" s="24"/>
+    </row>
+    <row r="53" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="20"/>
+      <c r="C53" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" s="24"/>
+    </row>
+    <row r="54" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="20"/>
+      <c r="C54" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="24"/>
+    </row>
+    <row r="55" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="20"/>
+      <c r="C55" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" s="24"/>
+    </row>
+    <row r="56" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="20"/>
+      <c r="C56" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E56" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G56" s="24"/>
+    </row>
+    <row r="57" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="20"/>
+      <c r="C57" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="24"/>
+    </row>
+    <row r="58" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="20"/>
+      <c r="C58" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" s="24"/>
+    </row>
+    <row r="59" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="20"/>
+      <c r="C59" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" s="24"/>
+    </row>
+    <row r="60" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="20"/>
+      <c r="C60" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E60" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F60" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" s="24"/>
+    </row>
+    <row r="61" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="20"/>
+      <c r="C61" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F61" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="24"/>
+    </row>
+    <row r="62" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="20"/>
+      <c r="C62" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G62" s="24"/>
+    </row>
+    <row r="63" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="20"/>
+      <c r="C63" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" s="24"/>
+    </row>
+    <row r="64" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="20"/>
+      <c r="C64" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="24"/>
+    </row>
+    <row r="65" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="20"/>
+      <c r="C65" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="24"/>
+    </row>
+    <row r="66" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="20"/>
+      <c r="C66" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" s="24"/>
+    </row>
+    <row r="67" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="20"/>
+      <c r="C67" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G67" s="24"/>
+    </row>
+    <row r="68" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="20"/>
+      <c r="C68" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D68" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" s="24"/>
+    </row>
+    <row r="69" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C69" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="26" t="s">
+      <c r="D69" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E53" s="21" t="s">
+      <c r="E69" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F53" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="22" t="s">
+      <c r="F69" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="18"/>
-      <c r="C54" s="27" t="s">
+    <row r="70" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="20"/>
+      <c r="C70" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D54" s="26" t="s">
+      <c r="D70" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="21" t="s">
+      <c r="E70" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F54" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G54" s="22"/>
-    </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="18"/>
-      <c r="C55" s="27" t="s">
+      <c r="F70" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="24"/>
+    </row>
+    <row r="71" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="20"/>
+      <c r="C71" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="26" t="s">
+      <c r="D71" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E71" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F55" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G55" s="22"/>
-    </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="18"/>
-      <c r="C56" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D56" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E56" s="21" t="s">
+      <c r="F71" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" s="24"/>
+    </row>
+    <row r="72" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="20"/>
+      <c r="C72" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E72" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F56" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G56" s="22"/>
-    </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="18"/>
-      <c r="C57" s="27" t="s">
+      <c r="F72" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G72" s="24"/>
+    </row>
+    <row r="73" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="20"/>
+      <c r="C73" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D57" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E57" s="21" t="s">
+      <c r="D73" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E73" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F57" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G57" s="22"/>
-    </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="18"/>
-      <c r="C58" s="27" t="s">
+      <c r="F73" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G73" s="24"/>
+    </row>
+    <row r="74" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="20"/>
+      <c r="C74" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D74" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E58" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58" s="22"/>
-    </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="18"/>
-      <c r="C59" s="27" t="s">
+      <c r="E74" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G74" s="24"/>
+    </row>
+    <row r="75" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="20"/>
+      <c r="C75" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="26" t="s">
+      <c r="D75" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E59" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" s="22" t="s">
+      <c r="E75" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G59" s="22"/>
-    </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="18"/>
-      <c r="C60" s="27" t="s">
+      <c r="G75" s="24"/>
+    </row>
+    <row r="76" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="20"/>
+      <c r="C76" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D76" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="E60" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F60" s="22" t="s">
+      <c r="E76" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G60" s="22"/>
-    </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="18"/>
-      <c r="C61" s="27" t="s">
+      <c r="G76" s="24"/>
+    </row>
+    <row r="77" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="20"/>
+      <c r="C77" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="D77" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="E61" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F61" s="22" t="s">
+      <c r="E77" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G61" s="22"/>
-    </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="18"/>
-      <c r="C62" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F62" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G62" s="22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="18"/>
-      <c r="C63" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D63" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G63" s="22"/>
-    </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="18"/>
-      <c r="C64" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D64" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64" s="22"/>
-    </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="18"/>
-      <c r="C65" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D65" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E65" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F65" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65" s="22"/>
-    </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B66" s="18"/>
-      <c r="C66" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D66" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="E66" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66" s="22"/>
-    </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="18"/>
-      <c r="C67" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D67" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E67" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F67" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G67" s="22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B68" s="18"/>
-      <c r="C68" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F68" s="22" t="s">
+      <c r="G77" s="24"/>
+    </row>
+    <row r="78" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="20"/>
+      <c r="C78" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="E78" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F78" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="20"/>
+      <c r="C79" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E79" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G79" s="24"/>
+    </row>
+    <row r="80" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="20"/>
+      <c r="C80" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E80" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="24"/>
+    </row>
+    <row r="81" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="20"/>
+      <c r="C81" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D81" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G81" s="24"/>
+    </row>
+    <row r="82" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="20"/>
+      <c r="C82" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E82" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" s="24"/>
+    </row>
+    <row r="83" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="20"/>
+      <c r="C83" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D83" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G83" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="20"/>
+      <c r="C84" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E84" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F84" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G68" s="22"/>
-    </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B69" s="18"/>
-      <c r="C69" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F69" s="22" t="s">
+      <c r="G84" s="24"/>
+    </row>
+    <row r="85" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="20"/>
+      <c r="C85" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E85" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G69" s="22" t="n">
+      <c r="G85" s="24" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B70" s="18"/>
-      <c r="C70" s="27" t="s">
+    <row r="86" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="20"/>
+      <c r="C86" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D70" s="26" t="s">
+      <c r="D86" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="E70" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F70" s="22" t="s">
+      <c r="E86" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G70" s="22"/>
-    </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B71" s="18"/>
-      <c r="C71" s="27" t="s">
+      <c r="G86" s="24"/>
+    </row>
+    <row r="87" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="20"/>
+      <c r="C87" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="E71" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F71" s="22" t="s">
+      <c r="D87" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F87" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G71" s="22" t="s">
+      <c r="G87" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B72" s="18"/>
-      <c r="C72" s="27" t="s">
+    <row r="88" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="20"/>
+      <c r="C88" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D72" s="26" t="s">
+      <c r="D88" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E72" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F72" s="22" t="s">
+      <c r="E88" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F88" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G72" s="22" t="s">
+      <c r="G88" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B73" s="18"/>
-      <c r="C73" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D73" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F73" s="22" t="s">
+    <row r="89" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="20"/>
+      <c r="C89" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F89" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G73" s="22" t="s">
+      <c r="G89" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B74" s="18"/>
-      <c r="C74" s="27" t="s">
+    <row r="90" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="20"/>
+      <c r="C90" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="26" t="s">
+      <c r="D90" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E74" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F74" s="22" t="s">
+      <c r="E90" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F90" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G74" s="22"/>
-    </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B75" s="18"/>
-      <c r="C75" s="27" t="s">
+      <c r="G90" s="24"/>
+    </row>
+    <row r="91" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="20"/>
+      <c r="C91" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D75" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E75" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F75" s="22" t="s">
+      <c r="D91" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E91" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F91" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G75" s="22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B76" s="18"/>
-      <c r="C76" s="27" t="s">
+      <c r="G91" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="20"/>
+      <c r="C92" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D76" s="26" t="s">
+      <c r="D92" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="E76" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F76" s="22" t="s">
+      <c r="E92" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G76" s="22"/>
-    </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B77" s="18" t="s">
+      <c r="G92" s="24"/>
+    </row>
+    <row r="93" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="27" t="s">
+      <c r="C93" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D77" s="26" t="s">
+      <c r="D93" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E77" s="21" t="s">
+      <c r="E93" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F77" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G77" s="22" t="s">
+      <c r="F93" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G93" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B78" s="18"/>
-      <c r="C78" s="27" t="s">
+    <row r="94" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="20"/>
+      <c r="C94" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D78" s="26" t="s">
+      <c r="D94" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E78" s="21" t="s">
+      <c r="E94" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F78" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G78" s="22"/>
-    </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="18"/>
-      <c r="C79" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D79" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E79" s="21" t="s">
+      <c r="F94" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="24"/>
+    </row>
+    <row r="95" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="20"/>
+      <c r="C95" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D95" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E95" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F79" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G79" s="22"/>
-    </row>
-    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B80" s="18"/>
-      <c r="C80" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="D80" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="E80" s="21" t="s">
+      <c r="F95" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="24"/>
+    </row>
+    <row r="96" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="20"/>
+      <c r="C96" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D96" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="E96" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F80" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G80" s="22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B81" s="18"/>
-      <c r="C81" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="D81" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="E81" s="21" t="s">
+      <c r="F96" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="20"/>
+      <c r="C97" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D97" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E97" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F81" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G81" s="22"/>
-    </row>
-    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B82" s="18"/>
-      <c r="C82" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D82" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="E82" s="21" t="s">
+      <c r="F97" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" s="24"/>
+    </row>
+    <row r="98" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="20"/>
+      <c r="C98" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D98" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="E98" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F82" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G82" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B83" s="18"/>
-      <c r="C83" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D83" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E83" s="21" t="s">
+      <c r="F98" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="20"/>
+      <c r="C99" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D99" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="E99" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F83" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G83" s="22"/>
-    </row>
-    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B84" s="18"/>
-      <c r="C84" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D84" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="E84" s="21" t="s">
+      <c r="F99" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" s="24"/>
+    </row>
+    <row r="100" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="20"/>
+      <c r="C100" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D100" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E100" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F84" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G84" s="22" t="s">
+      <c r="F100" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B85" s="18"/>
-      <c r="C85" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D85" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E85" s="21" t="s">
+    <row r="101" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="20"/>
+      <c r="C101" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D101" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E101" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F85" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G85" s="22" t="s">
+      <c r="F101" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G101" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B86" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C86" s="27" t="s">
+    <row r="102" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D86" s="26" t="s">
+      <c r="D102" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E86" s="21" t="s">
+      <c r="E102" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F86" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G86" s="22"/>
-    </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B87" s="18"/>
-      <c r="C87" s="27" t="s">
+      <c r="F102" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" s="24"/>
+    </row>
+    <row r="103" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="20"/>
+      <c r="C103" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D87" s="26" t="s">
+      <c r="D103" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E87" s="21" t="s">
+      <c r="E103" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F87" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G87" s="22"/>
-    </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B88" s="18"/>
-      <c r="C88" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="D88" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E88" s="21" t="s">
+      <c r="F103" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" s="24"/>
+    </row>
+    <row r="104" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="20"/>
+      <c r="C104" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D104" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E104" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F88" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G88" s="22"/>
-    </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B89" s="18"/>
-      <c r="C89" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D89" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E89" s="21" t="s">
+      <c r="F104" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104" s="24"/>
+    </row>
+    <row r="105" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="20"/>
+      <c r="C105" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D105" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="E105" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F89" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G89" s="22"/>
-    </row>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="18"/>
-      <c r="C90" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="D90" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="E90" s="21" t="s">
+      <c r="F105" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G105" s="24"/>
+    </row>
+    <row r="106" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="20"/>
+      <c r="C106" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D106" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E106" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F90" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G90" s="22"/>
-    </row>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B91" s="18"/>
-      <c r="C91" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="D91" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E91" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F91" s="22" t="s">
+      <c r="F106" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="24"/>
+    </row>
+    <row r="107" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="20"/>
+      <c r="C107" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D107" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E107" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F107" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G91" s="22"/>
-    </row>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="18"/>
-      <c r="C92" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="D92" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E92" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F92" s="22" t="s">
+      <c r="G107" s="24"/>
+    </row>
+    <row r="108" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="20"/>
+      <c r="C108" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D108" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E108" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F108" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G92" s="22"/>
-    </row>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="18"/>
-      <c r="C93" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D93" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E93" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F93" s="22" t="s">
+      <c r="G108" s="24"/>
+    </row>
+    <row r="109" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="20"/>
+      <c r="C109" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D109" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="E109" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F109" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G93" s="22"/>
-    </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="18"/>
-      <c r="C94" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D94" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F94" s="22" t="s">
+      <c r="G109" s="24"/>
+    </row>
+    <row r="110" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="20"/>
+      <c r="C110" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D110" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="E110" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F110" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G94" s="22"/>
-    </row>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B95" s="18"/>
-      <c r="C95" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="D95" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="E95" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F95" s="22" t="s">
+      <c r="G110" s="24"/>
+    </row>
+    <row r="111" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="20"/>
+      <c r="C111" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D111" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E111" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F111" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G95" s="22"/>
-    </row>
-    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B96" s="18"/>
-      <c r="C96" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="D96" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E96" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F96" s="22" t="s">
+      <c r="G111" s="24"/>
+    </row>
+    <row r="112" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="20"/>
+      <c r="C112" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D112" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="E112" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F112" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G96" s="22"/>
-    </row>
-    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B97" s="18"/>
-      <c r="C97" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D97" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="E97" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F97" s="22" t="s">
+      <c r="G112" s="24"/>
+    </row>
+    <row r="113" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="20"/>
+      <c r="C113" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D113" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E113" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F113" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G97" s="22"/>
-    </row>
-    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B98" s="18"/>
-      <c r="C98" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="D98" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="E98" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F98" s="22" t="s">
+      <c r="G113" s="24"/>
+    </row>
+    <row r="114" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="20"/>
+      <c r="C114" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D114" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="E114" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F114" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G98" s="22"/>
-    </row>
-    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B99" s="18"/>
-      <c r="C99" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="D99" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E99" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F99" s="22" t="s">
+      <c r="G114" s="24"/>
+    </row>
+    <row r="115" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="20"/>
+      <c r="C115" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D115" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E115" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F115" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G99" s="22"/>
-    </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B100" s="18"/>
-      <c r="C100" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="D100" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="E100" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F100" s="22" t="s">
+      <c r="G115" s="24"/>
+    </row>
+    <row r="116" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="20"/>
+      <c r="C116" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D116" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E116" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F116" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G100" s="22"/>
-    </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B101" s="18"/>
-      <c r="C101" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="D101" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="E101" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F101" s="22" t="s">
+      <c r="G116" s="24"/>
+    </row>
+    <row r="117" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="20"/>
+      <c r="C117" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D117" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="E117" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G101" s="22"/>
-    </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B102" s="18"/>
-      <c r="C102" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="D102" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="E102" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F102" s="22" t="s">
+      <c r="G117" s="24"/>
+    </row>
+    <row r="118" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="20"/>
+      <c r="C118" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D118" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="E118" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F118" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G102" s="22"/>
-    </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B103" s="18"/>
-      <c r="C103" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="D103" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="E103" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F103" s="22" t="s">
+      <c r="G118" s="24"/>
+    </row>
+    <row r="119" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="20"/>
+      <c r="C119" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D119" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E119" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F119" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G103" s="22"/>
-    </row>
-    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B104" s="18"/>
-      <c r="C104" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="D104" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="E104" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F104" s="22" t="s">
+      <c r="G119" s="24"/>
+    </row>
+    <row r="120" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="20"/>
+      <c r="C120" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="D120" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E120" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F120" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="G104" s="22"/>
-    </row>
-    <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="G120" s="24"/>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B21:B26"/>
-    <mergeCell ref="B27:B52"/>
-    <mergeCell ref="B53:B76"/>
-    <mergeCell ref="B77:B85"/>
-    <mergeCell ref="B86:B104"/>
+    <mergeCell ref="B27:B68"/>
+    <mergeCell ref="B69:B92"/>
+    <mergeCell ref="B93:B101"/>
+    <mergeCell ref="B102:B120"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5496,11 +5875,12 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="27.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="27" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5524,25 +5904,25 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Import/Export" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Import/Export" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A1002" type="list">
       <formula1>Lookup_Table!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5566,259 +5946,1211 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AN1048576"/>
+  <dimension ref="A1:AS1048576"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="6.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="27.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="11.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="20.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="15.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="14.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="20.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="10.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="15.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="25.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="15.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="16.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="22.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="25.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="16.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="25.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="14.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="27" width="9.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="27" width="17.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="27" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="27" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="27" width="27.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="27" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="27" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="11.39"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="27" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="27" width="15.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="18.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="16.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="27" width="17.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="10.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="27" width="15.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="21.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="27" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="27" width="16.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="27" width="10.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="27" width="15.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="25.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="27" width="16.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="27" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="25.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="27" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="27" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="19.59"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="true" ht="61.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
+    <row r="1" s="30" customFormat="true" ht="61.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="I1" s="30" t="s">
+      <c r="G1" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="31" t="s">
+      <c r="T1" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="U1" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="V1" s="31" t="s">
+      <c r="V1" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="W1" s="31" t="s">
+      <c r="W1" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="X1" s="31" t="s">
+      <c r="X1" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="Y1" s="31" t="s">
+      <c r="Y1" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="Z1" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA1" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB1" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="AC1" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="AD1" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE1" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF1" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="AG1" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="AH1" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="AI1" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="AJ1" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="AK1" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="AL1" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="AM1" s="31" t="s">
+      <c r="Z1" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA1" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB1" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC1" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD1" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE1" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF1" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG1" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH1" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI1" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ1" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK1" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL1" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM1" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN1" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO1" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="AP1" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="AN1" s="31" t="s">
-        <v>184</v>
-      </c>
+      <c r="AQ1" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>187</v>
-      </c>
-      <c r="I2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="O2" s="29" t="s">
+      <c r="K2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="P2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="T2" s="0" t="s">
-        <v>192</v>
+      <c r="Q2" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="T2" s="27"/>
+      <c r="Z2" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="I3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="N3" s="29" t="s">
+      <c r="K3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="N3" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="P3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="R3" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="T3" s="0" t="s">
-        <v>192</v>
-      </c>
+      <c r="Q3" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="R3" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="T3" s="27"/>
+      <c r="Z3" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T4" s="27"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T5" s="27"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T7" s="27"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T8" s="27"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T9" s="27"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T10" s="27"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T11" s="27"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T12" s="27"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T13" s="27"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T14" s="27"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T15" s="27"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T16" s="27"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T17" s="27"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T18" s="27"/>
+      <c r="Y18" s="29"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T19" s="27"/>
+      <c r="Y19" s="29"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T20" s="27"/>
+      <c r="Y20" s="29"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T21" s="27"/>
+      <c r="Y21" s="29"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T22" s="27"/>
+      <c r="Y22" s="29"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T23" s="27"/>
+      <c r="Y23" s="29"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T24" s="27"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T25" s="27"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T26" s="27"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T27" s="27"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T28" s="27"/>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T29" s="27"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T30" s="27"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T31" s="27"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T32" s="27"/>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T33" s="27"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T34" s="27"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T35" s="27"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T36" s="27"/>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T37" s="27"/>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T38" s="27"/>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T39" s="27"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T40" s="27"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T41" s="27"/>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T42" s="27"/>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T43" s="27"/>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T44" s="27"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T45" s="27"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T46" s="27"/>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T47" s="27"/>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T48" s="27"/>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T49" s="27"/>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T50" s="27"/>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T51" s="27"/>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T52" s="27"/>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T53" s="27"/>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T54" s="27"/>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T55" s="27"/>
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T56" s="27"/>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T57" s="27"/>
+    </row>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T58" s="27"/>
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T59" s="27"/>
+    </row>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T60" s="27"/>
+    </row>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T61" s="27"/>
+    </row>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T62" s="27"/>
+    </row>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T63" s="27"/>
+    </row>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T64" s="27"/>
+    </row>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T65" s="27"/>
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T66" s="27"/>
+    </row>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T67" s="27"/>
+    </row>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T68" s="27"/>
+    </row>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T69" s="27"/>
+    </row>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T70" s="27"/>
+    </row>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T71" s="27"/>
+    </row>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T72" s="27"/>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T73" s="27"/>
+    </row>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T74" s="27"/>
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T75" s="27"/>
+    </row>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T76" s="27"/>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T77" s="27"/>
+    </row>
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T78" s="27"/>
+    </row>
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T79" s="27"/>
+    </row>
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T80" s="27"/>
+    </row>
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T81" s="27"/>
+    </row>
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T82" s="27"/>
+    </row>
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T83" s="27"/>
+    </row>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T84" s="27"/>
+    </row>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T85" s="27"/>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T86" s="27"/>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T87" s="27"/>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T88" s="27"/>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T89" s="27"/>
+    </row>
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T90" s="27"/>
+    </row>
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T91" s="27"/>
+    </row>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T92" s="27"/>
+    </row>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T93" s="27"/>
+    </row>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T94" s="27"/>
+    </row>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T95" s="27"/>
+    </row>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T96" s="27"/>
+    </row>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T97" s="27"/>
+    </row>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T98" s="27"/>
+    </row>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T99" s="27"/>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T100" s="27"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T101" s="27"/>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T102" s="27"/>
+    </row>
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T103" s="27"/>
+    </row>
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T104" s="27"/>
+    </row>
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T105" s="27"/>
+    </row>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T106" s="27"/>
+    </row>
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T107" s="27"/>
+    </row>
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T108" s="27"/>
+    </row>
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T109" s="27"/>
+    </row>
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T110" s="27"/>
+    </row>
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T111" s="27"/>
+    </row>
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T112" s="27"/>
+    </row>
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T113" s="27"/>
+    </row>
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T114" s="27"/>
+    </row>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T115" s="27"/>
+    </row>
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T116" s="27"/>
+    </row>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T117" s="27"/>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T118" s="27"/>
+    </row>
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T119" s="27"/>
+    </row>
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T120" s="27"/>
+    </row>
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T121" s="27"/>
+    </row>
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T122" s="27"/>
+    </row>
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T123" s="27"/>
+    </row>
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T124" s="27"/>
+    </row>
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T125" s="27"/>
+    </row>
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T126" s="27"/>
+    </row>
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T127" s="27"/>
+    </row>
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T128" s="27"/>
+    </row>
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T129" s="27"/>
+    </row>
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T130" s="27"/>
+    </row>
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T131" s="27"/>
+    </row>
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T132" s="27"/>
+    </row>
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T133" s="27"/>
+    </row>
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T134" s="27"/>
+    </row>
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T135" s="27"/>
+    </row>
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T136" s="27"/>
+    </row>
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T137" s="27"/>
+    </row>
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T138" s="27"/>
+    </row>
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T139" s="27"/>
+    </row>
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T140" s="27"/>
+    </row>
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T141" s="27"/>
+    </row>
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T142" s="27"/>
+    </row>
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T143" s="27"/>
+    </row>
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T144" s="27"/>
+    </row>
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T145" s="27"/>
+    </row>
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T146" s="27"/>
+    </row>
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T147" s="27"/>
+    </row>
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T148" s="27"/>
+    </row>
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T149" s="27"/>
+    </row>
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T150" s="27"/>
+    </row>
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T151" s="27"/>
+    </row>
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T152" s="27"/>
+    </row>
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T153" s="27"/>
+    </row>
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T154" s="27"/>
+    </row>
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T155" s="27"/>
+    </row>
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T156" s="27"/>
+    </row>
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T157" s="27"/>
+    </row>
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T158" s="27"/>
+    </row>
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T159" s="27"/>
+    </row>
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T160" s="27"/>
+    </row>
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T161" s="27"/>
+    </row>
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T162" s="27"/>
+    </row>
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T163" s="27"/>
+    </row>
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T164" s="27"/>
+    </row>
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T165" s="27"/>
+    </row>
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T166" s="27"/>
+    </row>
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T167" s="27"/>
+    </row>
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T168" s="27"/>
+    </row>
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T169" s="27"/>
+    </row>
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T170" s="27"/>
+    </row>
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T171" s="27"/>
+    </row>
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T172" s="27"/>
+    </row>
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T173" s="27"/>
+    </row>
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T174" s="27"/>
+    </row>
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T175" s="27"/>
+    </row>
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T176" s="27"/>
+    </row>
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T177" s="27"/>
+    </row>
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T178" s="27"/>
+    </row>
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T179" s="27"/>
+    </row>
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T180" s="27"/>
+    </row>
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T181" s="27"/>
+    </row>
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T182" s="27"/>
+    </row>
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T183" s="27"/>
+    </row>
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T184" s="27"/>
+    </row>
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T185" s="27"/>
+    </row>
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T186" s="27"/>
+    </row>
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T187" s="27"/>
+    </row>
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T188" s="27"/>
+    </row>
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T189" s="27"/>
+    </row>
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T190" s="27"/>
+    </row>
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T191" s="27"/>
+    </row>
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T192" s="27"/>
+    </row>
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T193" s="27"/>
+    </row>
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T194" s="27"/>
+    </row>
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T195" s="27"/>
+    </row>
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T196" s="27"/>
+    </row>
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T197" s="27"/>
+    </row>
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T198" s="27"/>
+    </row>
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T199" s="27"/>
+    </row>
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T200" s="27"/>
+    </row>
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T201" s="27"/>
+    </row>
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T202" s="27"/>
+    </row>
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T203" s="27"/>
+    </row>
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T204" s="27"/>
+    </row>
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T205" s="27"/>
+    </row>
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T206" s="27"/>
+    </row>
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T207" s="27"/>
+    </row>
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T208" s="27"/>
+    </row>
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T209" s="27"/>
+    </row>
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T210" s="27"/>
+    </row>
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T211" s="27"/>
+    </row>
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T212" s="27"/>
+    </row>
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T213" s="27"/>
+    </row>
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T214" s="27"/>
+    </row>
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T215" s="27"/>
+    </row>
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T216" s="27"/>
+    </row>
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T217" s="27"/>
+    </row>
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T218" s="27"/>
+    </row>
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T219" s="27"/>
+    </row>
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T220" s="27"/>
+    </row>
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T221" s="27"/>
+    </row>
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T222" s="27"/>
+    </row>
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T223" s="27"/>
+    </row>
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T224" s="27"/>
+    </row>
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T225" s="27"/>
+    </row>
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T226" s="27"/>
+    </row>
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T227" s="27"/>
+    </row>
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T228" s="27"/>
+    </row>
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T229" s="27"/>
+    </row>
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T230" s="27"/>
+    </row>
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T231" s="27"/>
+    </row>
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T232" s="27"/>
+    </row>
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T233" s="27"/>
+    </row>
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T234" s="27"/>
+    </row>
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T235" s="27"/>
+    </row>
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T236" s="27"/>
+    </row>
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T237" s="27"/>
+    </row>
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T238" s="27"/>
+    </row>
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T239" s="27"/>
+    </row>
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T240" s="27"/>
+    </row>
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T241" s="27"/>
+    </row>
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T242" s="27"/>
+    </row>
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T243" s="27"/>
+    </row>
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T244" s="27"/>
+    </row>
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T245" s="27"/>
+    </row>
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T246" s="27"/>
+    </row>
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T247" s="27"/>
+    </row>
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T248" s="27"/>
+    </row>
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T249" s="27"/>
+    </row>
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T250" s="27"/>
+    </row>
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T251" s="27"/>
+    </row>
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T252" s="27"/>
+    </row>
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T253" s="27"/>
+    </row>
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T254" s="27"/>
+    </row>
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T255" s="27"/>
+    </row>
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T256" s="27"/>
+    </row>
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T257" s="27"/>
+    </row>
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T258" s="27"/>
+    </row>
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T259" s="27"/>
+    </row>
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T260" s="27"/>
+    </row>
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T261" s="27"/>
+    </row>
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T262" s="27"/>
+    </row>
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T263" s="27"/>
+    </row>
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T264" s="27"/>
+    </row>
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T265" s="27"/>
+    </row>
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T266" s="27"/>
+    </row>
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T267" s="27"/>
+    </row>
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T268" s="27"/>
+    </row>
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T269" s="27"/>
+    </row>
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T270" s="27"/>
+    </row>
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T271" s="27"/>
+    </row>
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T272" s="27"/>
+    </row>
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T273" s="27"/>
+    </row>
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T274" s="27"/>
+    </row>
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T275" s="27"/>
+    </row>
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T276" s="27"/>
+    </row>
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T277" s="27"/>
+    </row>
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T278" s="27"/>
+    </row>
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T279" s="27"/>
+    </row>
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T280" s="27"/>
+    </row>
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T281" s="27"/>
+    </row>
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T282" s="27"/>
+    </row>
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T283" s="27"/>
+    </row>
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T284" s="27"/>
+    </row>
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T285" s="27"/>
+    </row>
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T286" s="27"/>
+    </row>
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T287" s="27"/>
+    </row>
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T288" s="27"/>
+    </row>
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T289" s="27"/>
+    </row>
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T290" s="27"/>
+    </row>
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T291" s="27"/>
+    </row>
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T292" s="27"/>
+    </row>
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T293" s="27"/>
+    </row>
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T294" s="27"/>
+    </row>
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T295" s="27"/>
+    </row>
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T296" s="27"/>
+    </row>
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T297" s="27"/>
+    </row>
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T298" s="27"/>
+    </row>
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T299" s="27"/>
+    </row>
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T300" s="27"/>
+    </row>
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T301" s="27"/>
+    </row>
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T302" s="27"/>
+    </row>
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T303" s="27"/>
+    </row>
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T304" s="27"/>
+    </row>
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T305" s="27"/>
+    </row>
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T306" s="27"/>
+    </row>
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T307" s="27"/>
+    </row>
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T308" s="27"/>
+    </row>
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T309" s="27"/>
+    </row>
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T310" s="27"/>
+    </row>
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T311" s="27"/>
+    </row>
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T312" s="27"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:AN3"/>
-  <dataValidations count="10">
+  <autoFilter ref="A1:AQ3"/>
+  <dataValidations count="18">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J3" type="whole">
       <formula1>1</formula1>
       <formula2>65500</formula2>
@@ -5827,36 +7159,68 @@
       <formula1>1</formula1>
       <formula2>96</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D1003" type="list">
       <formula1>Lookup_Table!$A$2:$A$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:P3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O313 T2:T312 O314:O1003" type="list">
       <formula1>Lookup_Table!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="Q2:Q3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="Q2:Q1003" type="list">
       <formula1>Lookup_Table!$E$2:$E$202</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="R2:R3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="R2:R1003" type="list">
       <formula1>Lookup_Table!$J$2:$J$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N1003" type="list">
       <formula1>Lookup_Table!$G$2:$G$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L1003" type="list">
       <formula1>Lookup_Table!$AD$2:$AD$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A1003" type="list">
       <formula1>Lookup_Table!$C$2:$C$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2:B1003" type="list">
       <formula1>NGM!$B$2:$B2500</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="P2:P1003 V2:V1003 Z2:Z1003 AD2:AD1003 AF2:AF1003 AO2:AO1003" type="list">
+      <formula1>Lookup_Table!$C$2:$C$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="W2:W1003" type="list">
+      <formula1>Lookup_Table!$AF$2:$AF$8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AE2:AE1003" type="list">
+      <formula1>Lookup_Table!$AH$2:$AH$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AG2:AG1003" type="list">
+      <formula1>Lookup_Table!$AI$2:$AI$4</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AJ2:AJ1003" type="list">
+      <formula1>Lookup_Table!$AJ$2:$AJ$4</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AK2:AK1003" type="list">
+      <formula1>Lookup_Table!$AK$2:$AK$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AM2:AM1003" type="list">
+      <formula1>Lookup_Table!$AL$2:$AL$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AB2:AB1003" type="list">
+      <formula1>Lookup_Table!$AG$2:$AG$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -5883,24 +7247,24 @@
   <dimension ref="A1:W1048576"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="11.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="37.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="26.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="23.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="45.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="37.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="26.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="23.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="45.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5914,7 +7278,7 @@
         <v>44</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E1" s="28" t="s">
         <v>46</v>
@@ -5935,28 +7299,28 @@
         <v>60</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="O1" s="28" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="P1" s="28" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="Q1" s="28" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="R1" s="28" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="S1" s="28" t="s">
         <v>67</v>
@@ -5968,129 +7332,129 @@
         <v>72</v>
       </c>
       <c r="V1" s="28" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="W1" s="28" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="J2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="G2" s="31"/>
+      <c r="H2" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>115200</v>
       </c>
-      <c r="L2" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="N2" s="0" t="n">
+      <c r="L2" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q2" s="29" t="s">
+      <c r="P2" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="0" t="n">
+      <c r="R2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29" t="s">
+      <c r="S2" s="27"/>
+      <c r="T2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29" t="s">
+      <c r="U2" s="27"/>
+      <c r="V2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="29" t="s">
-        <v>190</v>
+      <c r="W2" s="27" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="23"/>
-      <c r="K3" s="0" t="n">
+      <c r="C3" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" s="31"/>
+      <c r="K3" s="1" t="n">
         <v>9600</v>
       </c>
-      <c r="L3" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="M3" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="N3" s="0" t="n">
+      <c r="L3" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q3" s="29" t="s">
+      <c r="P3" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29" t="s">
+      <c r="S3" s="27"/>
+      <c r="T3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29" t="s">
+      <c r="U3" s="27"/>
+      <c r="V3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="W3" s="29" t="s">
-        <v>204</v>
+      <c r="W3" s="27" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6169,12 +7533,12 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="27.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="16.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6185,111 +7549,111 @@
         <v>30</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="H2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>208</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="H3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>207</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="H4" s="0" t="s">
+      <c r="B4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6316,22 +7680,22 @@
   <dimension ref="A1:T11"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="5.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="15.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="13.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6342,322 +7706,322 @@
         <v>30</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="O1" s="28" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="P1" s="28" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="Q1" s="28" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="R1" s="28" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="S1" s="28" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="T1" s="28"/>
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="H2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="O2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="P2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="Q2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="R2" s="0" t="s">
+      <c r="R2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="S2" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>217</v>
+      <c r="C3" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>217</v>
+      <c r="C4" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>214</v>
+      <c r="A5" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>217</v>
+      <c r="C6" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="A7" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>217</v>
+      <c r="C7" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>214</v>
+      <c r="A8" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>222</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>217</v>
+      <c r="A9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>214</v>
+      <c r="A10" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>225</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>214</v>
+      <c r="A11" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -6678,1339 +8042,1404 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF177"/>
+  <dimension ref="A1:AL177"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="1.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="1.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="2.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="2.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="2.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="2.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="2.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="14.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="2.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="2.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="1.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="1.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="1.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="2.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="2.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="2.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="2.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>226</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="L1" s="0" t="s">
+      <c r="C1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="AA2" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AH2" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>9600</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="AH3" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>19200</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z4" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="P1" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="R1" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="T1" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="V1" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="X1" s="0" t="s">
-        <v>234</v>
-      </c>
-      <c r="Z1" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA1" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB1" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="AD1" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF1" s="0" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="H2" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="N2" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="P2" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="R2" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="T2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="V2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z2" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA2" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB2" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="AD2" s="0" t="s">
-        <v>236</v>
-      </c>
-      <c r="AF2" s="0" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>238</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>239</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <v>9600</v>
-      </c>
-      <c r="P3" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="R3" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="T3" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="V3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z3" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="AA3" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB3" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="AD3" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="AF3" s="0" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>250</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>251</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <v>19200</v>
-      </c>
-      <c r="P4" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="R4" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="T4" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="X4" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="Z4" s="0" t="s">
+      <c r="AA4" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="AG4" s="1"/>
+      <c r="AI4" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>57600</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="AG5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>38400</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AG6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>115200</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="AG7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>230400</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AG8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AA4" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB4" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="AF4" s="0" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>256</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>257</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <v>57600</v>
-      </c>
-      <c r="T5" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="X5" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="AF5" s="0" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>261</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>262</v>
-      </c>
-      <c r="L6" s="0" t="s">
-        <v>263</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <v>38400</v>
-      </c>
-      <c r="AF6" s="0" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>266</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <v>115200</v>
-      </c>
-      <c r="AF7" s="0" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="0" t="s">
-        <v>269</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>270</v>
-      </c>
-      <c r="N8" s="0" t="n">
-        <v>230400</v>
-      </c>
-      <c r="AF8" s="0" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="0" t="s">
-        <v>273</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="0" t="s">
-        <v>279</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="0" t="s">
-        <v>281</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="0" t="s">
-        <v>283</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="0" t="s">
-        <v>285</v>
-      </c>
-      <c r="L16" s="0" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="0" t="s">
-        <v>287</v>
-      </c>
-      <c r="L17" s="0" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="0" t="s">
-        <v>289</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="0" t="s">
-        <v>291</v>
-      </c>
-      <c r="L19" s="0" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="L20" s="0" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="0" t="s">
-        <v>295</v>
-      </c>
-      <c r="L21" s="0" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="0" t="s">
-        <v>297</v>
-      </c>
-      <c r="L22" s="0" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E23" s="0" t="s">
-        <v>299</v>
-      </c>
-      <c r="L23" s="0" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="0" t="s">
-        <v>301</v>
-      </c>
-      <c r="L24" s="0" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="L25" s="0" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="L26" s="0" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="0" t="s">
-        <v>307</v>
-      </c>
-      <c r="L27" s="0" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="L28" s="0" t="s">
-        <v>309</v>
+      <c r="L28" s="1" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="0" t="s">
-        <v>310</v>
-      </c>
-      <c r="L29" s="0" t="s">
-        <v>311</v>
+      <c r="E29" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E30" s="0" t="s">
-        <v>312</v>
-      </c>
-      <c r="L30" s="0" t="s">
-        <v>313</v>
+      <c r="E30" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="L31" s="0" t="s">
-        <v>315</v>
+      <c r="E31" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="L32" s="0" t="s">
-        <v>317</v>
+      <c r="E32" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="0" t="s">
-        <v>318</v>
-      </c>
-      <c r="L33" s="0" t="s">
-        <v>319</v>
+      <c r="E33" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E34" s="0" t="s">
-        <v>320</v>
-      </c>
-      <c r="L34" s="0" t="s">
-        <v>321</v>
+      <c r="E34" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E35" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="L35" s="0" t="s">
-        <v>323</v>
+      <c r="E35" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E36" s="0" t="s">
-        <v>324</v>
-      </c>
-      <c r="L36" s="0" t="s">
-        <v>325</v>
+      <c r="E36" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E37" s="0" t="s">
-        <v>326</v>
-      </c>
-      <c r="L37" s="0" t="s">
-        <v>327</v>
+      <c r="E37" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E38" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="L38" s="0" t="s">
-        <v>329</v>
+      <c r="E38" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E39" s="0" t="s">
-        <v>330</v>
-      </c>
-      <c r="L39" s="0" t="s">
-        <v>331</v>
+      <c r="E39" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E40" s="0" t="s">
-        <v>332</v>
-      </c>
-      <c r="L40" s="0" t="s">
-        <v>333</v>
+      <c r="E40" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E41" s="0" t="s">
-        <v>334</v>
-      </c>
-      <c r="L41" s="0" t="s">
-        <v>335</v>
+      <c r="E41" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E42" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="L42" s="0" t="s">
-        <v>337</v>
+      <c r="E42" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E43" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="L43" s="0" t="s">
-        <v>339</v>
+      <c r="E43" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E44" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="L44" s="0" t="s">
-        <v>341</v>
+      <c r="E44" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E45" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="L45" s="0" t="s">
-        <v>343</v>
+      <c r="E45" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E46" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="L46" s="0" t="s">
-        <v>345</v>
+      <c r="E46" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E47" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="L47" s="0" t="s">
-        <v>347</v>
+      <c r="E47" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E48" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="L48" s="0" t="s">
-        <v>349</v>
+      <c r="E48" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E49" s="0" t="s">
-        <v>350</v>
-      </c>
-      <c r="L49" s="0" t="s">
-        <v>351</v>
+      <c r="E49" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E50" s="0" t="s">
-        <v>352</v>
-      </c>
-      <c r="L50" s="0" t="s">
-        <v>353</v>
+      <c r="E50" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E51" s="0" t="s">
-        <v>354</v>
-      </c>
-      <c r="L51" s="0" t="s">
-        <v>355</v>
+      <c r="E51" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E52" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="L52" s="0" t="s">
-        <v>357</v>
+      <c r="E52" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E53" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="L53" s="0" t="s">
-        <v>359</v>
+      <c r="E53" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E54" s="0" t="s">
-        <v>360</v>
-      </c>
-      <c r="L54" s="0" t="s">
-        <v>361</v>
+      <c r="E54" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E55" s="0" t="s">
-        <v>362</v>
-      </c>
-      <c r="L55" s="0" t="s">
-        <v>363</v>
+      <c r="E55" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E56" s="0" t="s">
-        <v>364</v>
-      </c>
-      <c r="L56" s="0" t="s">
-        <v>365</v>
+      <c r="E56" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E57" s="0" t="s">
-        <v>366</v>
-      </c>
-      <c r="L57" s="0" t="s">
-        <v>367</v>
+      <c r="E57" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E58" s="0" t="s">
-        <v>368</v>
-      </c>
-      <c r="L58" s="0" t="s">
-        <v>369</v>
+      <c r="E58" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E59" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="L59" s="0" t="s">
-        <v>371</v>
+      <c r="E59" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E60" s="0" t="s">
-        <v>372</v>
-      </c>
-      <c r="L60" s="0" t="s">
-        <v>373</v>
+      <c r="E60" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E61" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="L61" s="0" t="s">
-        <v>375</v>
+      <c r="E61" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E62" s="0" t="s">
-        <v>376</v>
-      </c>
-      <c r="L62" s="0" t="s">
-        <v>377</v>
+      <c r="E62" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E63" s="0" t="s">
-        <v>378</v>
-      </c>
-      <c r="L63" s="0" t="s">
-        <v>379</v>
+      <c r="E63" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E64" s="0" t="s">
-        <v>380</v>
-      </c>
-      <c r="L64" s="0" t="s">
-        <v>381</v>
+      <c r="E64" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E65" s="0" t="s">
-        <v>382</v>
-      </c>
-      <c r="L65" s="0" t="s">
-        <v>383</v>
+      <c r="E65" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E66" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="L66" s="0" t="s">
-        <v>384</v>
+      <c r="E66" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L67" s="0" t="s">
-        <v>385</v>
+      <c r="L67" s="1" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L68" s="0" t="s">
-        <v>386</v>
+      <c r="L68" s="1" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L69" s="0" t="s">
-        <v>387</v>
+      <c r="L69" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L70" s="0" t="s">
-        <v>388</v>
+      <c r="L70" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L71" s="0" t="s">
-        <v>389</v>
+      <c r="L71" s="1" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L72" s="0" t="s">
-        <v>390</v>
+      <c r="L72" s="1" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L73" s="0" t="s">
-        <v>391</v>
+      <c r="L73" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L74" s="0" t="s">
-        <v>392</v>
+      <c r="L74" s="1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L75" s="0" t="s">
-        <v>393</v>
+      <c r="L75" s="1" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L76" s="0" t="s">
-        <v>394</v>
+      <c r="L76" s="1" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L77" s="0" t="s">
-        <v>395</v>
+      <c r="L77" s="1" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L78" s="0" t="s">
-        <v>396</v>
+      <c r="L78" s="1" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L79" s="0" t="s">
-        <v>397</v>
+      <c r="L79" s="1" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L80" s="0" t="s">
-        <v>398</v>
+      <c r="L80" s="1" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L81" s="0" t="s">
-        <v>399</v>
+      <c r="L81" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L82" s="0" t="s">
-        <v>400</v>
+      <c r="L82" s="1" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L83" s="0" t="s">
-        <v>401</v>
+      <c r="L83" s="1" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L84" s="0" t="s">
-        <v>402</v>
+      <c r="L84" s="1" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L85" s="0" t="s">
-        <v>403</v>
+      <c r="L85" s="1" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L86" s="0" t="s">
-        <v>404</v>
+      <c r="L86" s="1" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L87" s="0" t="s">
-        <v>405</v>
+      <c r="L87" s="1" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L88" s="0" t="s">
-        <v>406</v>
+      <c r="L88" s="1" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L89" s="0" t="s">
-        <v>407</v>
+      <c r="L89" s="1" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L90" s="0" t="s">
-        <v>408</v>
+      <c r="L90" s="1" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L91" s="0" t="s">
-        <v>409</v>
+      <c r="L91" s="1" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L92" s="0" t="s">
-        <v>410</v>
+      <c r="L92" s="1" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L93" s="0" t="s">
-        <v>411</v>
+      <c r="L93" s="1" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L94" s="0" t="s">
-        <v>412</v>
+      <c r="L94" s="1" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L95" s="0" t="s">
-        <v>413</v>
+      <c r="L95" s="1" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L96" s="0" t="s">
-        <v>414</v>
+      <c r="L96" s="1" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L97" s="0" t="s">
-        <v>415</v>
+      <c r="L97" s="1" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L98" s="0" t="s">
-        <v>416</v>
+      <c r="L98" s="1" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L99" s="0" t="s">
-        <v>417</v>
+      <c r="L99" s="1" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L100" s="0" t="s">
-        <v>418</v>
+      <c r="L100" s="1" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L101" s="0" t="s">
-        <v>419</v>
+      <c r="L101" s="1" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L102" s="0" t="s">
-        <v>420</v>
+      <c r="L102" s="1" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L103" s="0" t="s">
-        <v>421</v>
+      <c r="L103" s="1" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L104" s="0" t="s">
-        <v>422</v>
+      <c r="L104" s="1" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L105" s="0" t="s">
-        <v>423</v>
+      <c r="L105" s="1" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L106" s="0" t="s">
-        <v>424</v>
+      <c r="L106" s="1" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L107" s="0" t="s">
-        <v>425</v>
+      <c r="L107" s="1" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L108" s="0" t="s">
-        <v>426</v>
+      <c r="L108" s="1" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L109" s="0" t="s">
-        <v>427</v>
+      <c r="L109" s="1" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L110" s="0" t="s">
-        <v>428</v>
+      <c r="L110" s="1" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L111" s="0" t="s">
-        <v>429</v>
+      <c r="L111" s="1" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L112" s="0" t="s">
-        <v>430</v>
+      <c r="L112" s="1" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L113" s="0" t="s">
-        <v>431</v>
+      <c r="L113" s="1" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L114" s="0" t="s">
-        <v>432</v>
+      <c r="L114" s="1" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L115" s="0" t="s">
-        <v>433</v>
+      <c r="L115" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L116" s="0" t="s">
-        <v>434</v>
+      <c r="L116" s="1" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L117" s="0" t="s">
-        <v>435</v>
+      <c r="L117" s="1" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L118" s="0" t="s">
-        <v>436</v>
+      <c r="L118" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L119" s="0" t="s">
-        <v>437</v>
+      <c r="L119" s="1" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L120" s="0" t="s">
-        <v>438</v>
+      <c r="L120" s="1" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L121" s="0" t="s">
-        <v>439</v>
+      <c r="L121" s="1" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L122" s="0" t="s">
-        <v>440</v>
+      <c r="L122" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L123" s="0" t="s">
-        <v>441</v>
+      <c r="L123" s="1" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L124" s="0" t="s">
-        <v>442</v>
+      <c r="L124" s="1" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L125" s="0" t="s">
-        <v>443</v>
+      <c r="L125" s="1" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L126" s="0" t="s">
-        <v>444</v>
+      <c r="L126" s="1" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L127" s="0" t="s">
-        <v>445</v>
+      <c r="L127" s="1" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L128" s="0" t="s">
-        <v>446</v>
+      <c r="L128" s="1" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L129" s="0" t="s">
-        <v>447</v>
+      <c r="L129" s="1" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L130" s="0" t="s">
-        <v>448</v>
+      <c r="L130" s="1" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L131" s="0" t="s">
-        <v>449</v>
+      <c r="L131" s="1" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L132" s="0" t="s">
-        <v>450</v>
+      <c r="L132" s="1" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L133" s="0" t="s">
-        <v>451</v>
+      <c r="L133" s="1" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L134" s="0" t="s">
-        <v>452</v>
+      <c r="L134" s="1" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L135" s="0" t="s">
-        <v>453</v>
+      <c r="L135" s="1" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L136" s="0" t="s">
-        <v>454</v>
+      <c r="L136" s="1" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L137" s="0" t="s">
-        <v>455</v>
+      <c r="L137" s="1" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L138" s="0" t="s">
-        <v>456</v>
+      <c r="L138" s="1" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L139" s="0" t="s">
-        <v>457</v>
+      <c r="L139" s="1" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L140" s="0" t="s">
-        <v>458</v>
+      <c r="L140" s="1" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L141" s="0" t="s">
-        <v>459</v>
+      <c r="L141" s="1" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L142" s="0" t="s">
-        <v>460</v>
+      <c r="L142" s="1" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L143" s="0" t="s">
-        <v>461</v>
+      <c r="L143" s="1" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L144" s="0" t="s">
-        <v>462</v>
+      <c r="L144" s="1" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L145" s="0" t="s">
-        <v>463</v>
+      <c r="L145" s="1" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L146" s="0" t="s">
-        <v>464</v>
+      <c r="L146" s="1" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L147" s="0" t="s">
-        <v>465</v>
+      <c r="L147" s="1" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L148" s="0" t="s">
-        <v>466</v>
+      <c r="L148" s="1" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L149" s="0" t="s">
-        <v>467</v>
+      <c r="L149" s="1" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L150" s="0" t="s">
-        <v>468</v>
+      <c r="L150" s="1" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L151" s="0" t="s">
-        <v>469</v>
+      <c r="L151" s="1" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L152" s="0" t="s">
-        <v>470</v>
+      <c r="L152" s="1" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L153" s="0" t="s">
-        <v>471</v>
+      <c r="L153" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L154" s="0" t="s">
-        <v>472</v>
+      <c r="L154" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L155" s="0" t="s">
-        <v>473</v>
+      <c r="L155" s="1" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L156" s="0" t="s">
-        <v>474</v>
+      <c r="L156" s="1" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L157" s="0" t="s">
-        <v>475</v>
+      <c r="L157" s="1" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L158" s="0" t="s">
-        <v>476</v>
+      <c r="L158" s="1" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L159" s="0" t="s">
-        <v>477</v>
+      <c r="L159" s="1" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L160" s="0" t="s">
-        <v>478</v>
+      <c r="L160" s="1" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L161" s="0" t="s">
-        <v>479</v>
+      <c r="L161" s="1" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L162" s="0" t="s">
-        <v>480</v>
+      <c r="L162" s="1" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L163" s="0" t="s">
-        <v>481</v>
+      <c r="L163" s="1" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L164" s="0" t="s">
-        <v>482</v>
+      <c r="L164" s="1" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L165" s="0" t="s">
-        <v>483</v>
+      <c r="L165" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L166" s="0" t="s">
-        <v>484</v>
+      <c r="L166" s="1" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L167" s="0" t="s">
-        <v>485</v>
+      <c r="L167" s="1" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L168" s="0" t="s">
-        <v>486</v>
+      <c r="L168" s="1" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L169" s="0" t="s">
-        <v>487</v>
+      <c r="L169" s="1" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L170" s="0" t="s">
-        <v>488</v>
+      <c r="L170" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L171" s="0" t="s">
-        <v>489</v>
+      <c r="L171" s="1" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L172" s="0" t="s">
-        <v>490</v>
+      <c r="L172" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L173" s="0" t="s">
-        <v>491</v>
+      <c r="L173" s="1" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L174" s="0" t="s">
-        <v>492</v>
+      <c r="L174" s="1" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L175" s="0" t="s">
-        <v>493</v>
+      <c r="L175" s="1" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L176" s="0" t="s">
-        <v>494</v>
+      <c r="L176" s="1" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L177" s="0" t="s">
-        <v>495</v>
+      <c r="L177" s="1" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>
